--- a/doku/Einkaufsliste_HydroDesk_guenstig.xlsx
+++ b/doku/Einkaufsliste_HydroDesk_guenstig.xlsx
@@ -2860,72 +2860,76 @@
       <c r="P23" s="35" t="n"/>
     </row>
     <row r="24" ht="28.35" customHeight="1" s="25">
-      <c r="A24" s="27" t="n">
+      <c r="A24" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
         <is>
           <t>Step-Up 5 V</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>Berrybase</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="31" t="inlineStr">
         <is>
           <t>Pololu S13V10F5 5 V 1 A Step-Up/Step-Down</t>
         </is>
       </c>
-      <c r="E24" s="27" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>1 Stk</t>
         </is>
       </c>
-      <c r="F24" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="28" t="n">
+      <c r="F24" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="32" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="33">
         <f>G24/F24</f>
         <v/>
       </c>
-      <c r="I24" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="28">
+      <c r="I24" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="32">
         <f>ROUNDUP(I24/F24,0)*G24</f>
         <v/>
       </c>
-      <c r="K24" s="27" t="inlineStr">
+      <c r="K24" s="31" t="inlineStr">
         <is>
           <t>4,95 € DHL, frei ab 150 €</t>
         </is>
       </c>
-      <c r="L24" s="27" t="inlineStr">
+      <c r="L24" s="31" t="inlineStr">
         <is>
           <t>1–3 Tage</t>
         </is>
       </c>
-      <c r="M24" s="30" t="inlineStr">
+      <c r="M24" s="34" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/pololu-s13v10f5-5v-1a-step-up-step-down-converter</t>
         </is>
       </c>
-      <c r="N24" s="27" t="inlineStr">
+      <c r="N24" s="31" t="inlineStr">
         <is>
           <t>08.10.2026</t>
         </is>
       </c>
-      <c r="O24" s="27" t="inlineStr">
-        <is>
-          <t>EMPFOHLEN: fest 5 V, UVLO, Softstart, Überstromschutz; klein (ca. 9×12 mm) → im 37×17-Fach fixieren</t>
-        </is>
-      </c>
-      <c r="P24" s="27" t="n"/>
+      <c r="O24" s="31" t="inlineStr">
+        <is>
+          <t>GEWÄHLT in beiden Körben (08.10.2026): fest 5 V, 1 A, UVLO, Softstart, Überstromschutz; klein (ca. 9×12 mm) → im 37×17-Fach fixieren. Vergleich: Botland 7,90 € + Versand ab 4,99 € (eigener Shop, https://botland.de/aufwarts-abwartswandler/21022-s13v10f5-aufwarts-abwartswandler-5v-1a-pololu-4083.html), Eckstein 11,80 € – Berrybase ist im Korb am günstigsten, weil der Berrybase-Versand ohnehin anfällt</t>
+        </is>
+      </c>
+      <c r="P24" s="31" t="inlineStr">
+        <is>
+          <t>✔ günstigste</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="25">
       <c r="A25" s="27" t="n">
@@ -2996,76 +3000,72 @@
       <c r="P25" s="27" t="n"/>
     </row>
     <row r="26" ht="28.35" customHeight="1" s="25">
-      <c r="A26" s="31" t="n">
+      <c r="A26" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Step-Up 5 V</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>AliExpress</t>
         </is>
       </c>
-      <c r="D26" s="31" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>MT3608 Step-Up einstellbar (2 Stk)</t>
         </is>
       </c>
-      <c r="E26" s="31" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>2 Stk</t>
         </is>
       </c>
-      <c r="F26" s="31" t="n">
+      <c r="F26" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="32" t="n">
+      <c r="G26" s="37" t="n">
         <v>2.04</v>
       </c>
-      <c r="H26" s="33">
+      <c r="H26" s="38">
         <f>G26/F26</f>
         <v/>
       </c>
-      <c r="I26" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="32">
+      <c r="I26" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="37">
         <f>ROUNDUP(I26/F26,0)*G26</f>
         <v/>
       </c>
-      <c r="K26" s="31" t="inlineStr">
+      <c r="K26" s="35" t="inlineStr">
         <is>
           <t>lt. Liste '3+, kein Zollaufschlag'</t>
         </is>
       </c>
-      <c r="L26" s="31" t="inlineStr">
+      <c r="L26" s="35" t="inlineStr">
         <is>
           <t>1–3 Wochen</t>
         </is>
       </c>
-      <c r="M26" s="34" t="inlineStr">
+      <c r="M26" s="36" t="inlineStr">
         <is>
           <t>https://de.aliexpress.com/item/1005009806778521.html</t>
         </is>
       </c>
-      <c r="N26" s="31" t="inlineStr">
+      <c r="N26" s="35" t="inlineStr">
         <is>
           <t>08.10.2026</t>
         </is>
       </c>
-      <c r="O26" s="31" t="inlineStr">
-        <is>
-          <t>NUR MIT VORSICHT: Poti vorher auf 5,0 V stellen; bei 3,7→5 V real ca. 0,5 A, Ripple, heiß</t>
-        </is>
-      </c>
-      <c r="P26" s="31" t="inlineStr">
-        <is>
-          <t>✔ günstigste</t>
-        </is>
-      </c>
+      <c r="O26" s="35" t="inlineStr">
+        <is>
+          <t>GESTRICHEN 08.10.2026 (auch im günstigen Korb): bei 3,7→5 V real nur ca. 0,5 A – zu wenig für CYD (0,25–0,35 A) + 26 COB-LEDs (bis ca. 0,49 A); Poti, Ripple, heiß</t>
+        </is>
+      </c>
+      <c r="P26" s="35" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="25">
       <c r="A27" s="35" t="n">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="O27" s="35" t="inlineStr">
         <is>
-          <t>derzeit nicht verfügbar</t>
+          <t>derzeit nicht verfügbar; außerdem zu schwach (siehe Zeile darüber)</t>
         </is>
       </c>
       <c r="P27" s="35" t="n"/>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t>empfohlen statt MT3608</t>
+          <t>statt MT3608 (zu schwach, ca. 0,5 A bei 3,7 V)</t>
         </is>
       </c>
     </row>
@@ -5781,19 +5781,19 @@
       </c>
       <c r="C35" s="27" t="inlineStr">
         <is>
-          <t>AliExpress</t>
+          <t>Berrybase</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
         <is>
-          <t>MT3608 2 Stk (ab-Preis)</t>
+          <t>Pololu S13V10F5 5 V 1 A</t>
         </is>
       </c>
       <c r="E35" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>2.04</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G35" s="28">
         <f>E35*F35</f>
@@ -5801,12 +5801,12 @@
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>https://de.aliexpress.com/item/1005009806778521.html</t>
+          <t>https://www.berrybase.de/pololu-s13v10f5-5v-1a-step-up-step-down-converter</t>
         </is>
       </c>
       <c r="I35" s="27" t="inlineStr">
         <is>
-          <t>nur mit Vorsicht – Upgrade Pololu +9,95 €</t>
+          <t>statt MT3608 (08.10.2026): MT3608 liefert bei 3,7 V nur ca. 0,5 A – zu wenig für CYD + 26 COB-LEDs</t>
         </is>
       </c>
     </row>

--- a/doku/Einkaufsliste_HydroDesk_guenstig.xlsx
+++ b/doku/Einkaufsliste_HydroDesk_guenstig.xlsx
@@ -1082,12 +1082,12 @@
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>Nur nötig, wenn nicht an die SD-Pins gelötet wird</t>
+          <t>nicht bestellen, passt nicht. SD-Slot zeigt zur Frontwand (nur ca. 3,5 mm Luft); Sniffer würde ca. 35–40 mm herausstehen. GPIO18/19/23 direkt an den SD-Slot löten.</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>Pflicht*</t>
+          <t>gestrichen</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>Micro SD Sniffer TF-Adapter (1–3 Stk)</t>
+          <t>NICHT BESTELLEN – passt nicht ins Gehäuse</t>
         </is>
       </c>
       <c r="E42" s="33" t="inlineStr">
@@ -4453,7 +4453,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="34" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="H42" s="35">
         <f>G42/F42</f>
@@ -4462,9 +4462,10 @@
       <c r="I42" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="34">
-        <f>ROUNDUP(I42/F42,0)*G42</f>
-        <v/>
+      <c r="J42" s="34" t="inlineStr">
+        <is>
+          <t>nicht bestellen, passt nicht. SD-Slot zeigt zur Frontwand (nur ca. 3,5 mm Luft); Sniffer würde ca. 35–40 mm herausstehen. GPIO18/19/23 direkt an den SD-Slot löten.</t>
+        </is>
       </c>
       <c r="K42" s="33" t="inlineStr">
         <is>
@@ -7470,14 +7471,14 @@
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>Micro SD Sniffer (ab-Preis)</t>
+          <t>NICHT BESTELLEN – passt nicht</t>
         </is>
       </c>
       <c r="E49" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="30" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="G49" s="30">
         <f>E49*F49</f>
@@ -7490,7 +7491,7 @@
       </c>
       <c r="I49" s="29" t="inlineStr">
         <is>
-          <t>entfällt bei Löten</t>
+          <t>nicht bestellen, passt nicht. SD-Slot zeigt zur Frontwand (nur ca. 3,5 mm Luft); Sniffer würde ca. 35–40 mm herausstehen. GPIO18/19/23 direkt an den SD-Slot löten.</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8614,7 @@
     <row r="89" ht="15" customHeight="1" s="27">
       <c r="A89" s="51" t="inlineStr">
         <is>
-          <t>Nicht ermittelbar: Versandkosten alleschrauben.de; AliExpress-Preise der exakten Varianten; microSD-Sniffer und JST-1,25-4-pol.-Kabel in DE-Shops nicht gefunden.</t>
+          <t>Nicht ermittelbar: Versandkosten alleschrauben.de; AliExpress-Preise der exakten Varianten; JST-1,25-4-pol.-Kabel in DE-Shops nicht gefunden. microSD-Sniffer: nicht bestellen, passt nicht (SD-Slot→Front, 3,5 mm Luft; Sniffer ~35–40 mm) — GPIO18/19/23 direkt an den SD-Slot löten.</t>
         </is>
       </c>
     </row>
@@ -8691,1328 +8692,1321 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>HydroDesk Base V4 – Amazon-Bestellliste, Preise geprüft am 16.10.2026 (amazon.de, Lieferadresse DE)</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>A) Amazon – Pflicht (Versand durch Amazon)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Pos</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Teil</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Amazon-Titel</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>ASIN/Link</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Variante wählen</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>Packung</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t>passt weil</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="26" t="inlineStr">
         <is>
           <t>Hinweis</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>CYD ESP32-2432S028R 2,8"</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Fastsaw ESP32 Entwicklungsboard 2.8 Inch Touch TFT ILI9341 320x240</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B0G1N16Q16</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="26" t="inlineStr">
         <is>
           <t>„Colour Name“ 1 oder 2: Bild prüfen, Platine muss „ESP32-2432S028R“ heißen</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="26" t="n">
         <v>17.99</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="26" t="inlineStr">
         <is>
           <t>1 Stk</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t>ILI9341 2,8" Touch, 240 MHz, microSD-Slot, USB-C; Versand durch Amazon, auf Lager</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>Doku dünn (Rezension); 4-pol. JST-1,25-Kabel evtl. nicht dabei</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Wägezelle 5 kg + HX711</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>DIYmalls Wägezelle 5 kg + HX711</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B0B9H3YMT2</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>5 kg</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="26" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>1 Satz</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>TAL220-Bauform (80×12,7×12,7, M4/M5) wie in der SCAD; Versand durch Amazon</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>HX711-Stiftleiste selbst löten</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>COB-LED-Streifen WS2812B FCOB</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>BTF-LIGHTING WS2812B FCOB 1 m 160 LEDs/m 5 V</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B0H41MCVSW</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
         <is>
           <t>„1M 160LEDs/m 5mm“ (NICHT 180LEDs/10mm, nicht 5M)</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="26" t="n">
         <v>16.99</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>1 m</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="26" t="inlineStr">
         <is>
           <t>5 mm breit, 1 IC/LED, Schnitt alle 12,5 mm → 13 Segmente = 26 LEDs; Versand durch Amazon</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="26" t="inlineStr">
         <is>
           <t>Nur 18 auf Lager; 1 Rezension: Lötstellen schlecht → nach Lieferung prüfen</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>LiPo EEMB LP103454 2000 mAh</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
         <is>
           <t>EEMB 3,7V 2000mAh LiPo 103454 mit JST2.0-Stecker</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B08214DJLJ</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>1 Stück</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="26" t="n">
         <v>10.99</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr">
         <is>
           <t>1 Stk</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t>34,5×56×10,3 mm (Bild: 10,6) passt ins Akkufach; PCM-Schutz (Über-/Tiefentladung, Kurzschluss); JST-PHR-02</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="26" t="inlineStr">
         <is>
           <t>POLARITÄT vor dem Anstecken messen (rot=+ laut Seite, Rezensionen warnen)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>TC4056 USB-C Lader</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
         <is>
           <t>Dozylive 10 x TC4056 USB Type C Ladeplatine</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B0F67KYB4F</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>10er Pack</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="26" t="n">
         <v>6.99</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>10 Stk</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="26" t="inlineStr">
         <is>
           <t>4,2 V Ladeschluss, 1 A, Schutz 2,5 V; 10 Stück = Reserve</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="26" t="inlineStr">
         <is>
           <t>Länge nicht angegeben: Fach 26 mm → nachmessen; ohne CC-Widerstände lädt er nur mit USB-A→C-Kabel</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>Gummifüße Ø12</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>InLine Gummipads selbstklebend 12 mm schwarz, 20 Stück</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B09LDCTQGY</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>schwarz, 20 Stk</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="26" t="n">
         <v>5.45</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>20 Stk</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t>Ø12 mm (Mulde max. 13 mm), 3,6 mm hoch; Verkauf durch Amazon</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" s="26" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>Silikonmatte (auf 86×86 zuschneiden)</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>FICOFISE Silikonmatte 40x30 cm</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B0GVNMS4DZ</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>schwarz</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="26" t="n">
         <v>7.59</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>1 Matte</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t>1,2 mm dick (Soll 1–1,5 mm)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" s="26" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Schrauben M3×12 (8), M4 (2), M5×12 (2)</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>VIGRUE 1120 tlg. Senkkopf Innensechskant A2 M3–M6</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B09XQMQNYY</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="26" t="n">
         <v>26.59</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>1120 tlg.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="26" t="inlineStr">
         <is>
           <t>enthält M3×12, M4×12, M5×12 Senkkopf Innensechskant</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>M4×12 statt ×10: geprüft in SCAD, Spitze bleibt in der 12,7-mm-Wägezelle (ca. 7,4 mm Eingriff) → passt. Teuer: alleschrauben.de ca. 4,86 € + Versand</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr"/>
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>Summe A</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
+      <c r="C13" s="26" t="inlineStr"/>
+      <c r="D13" s="26" t="inlineStr"/>
+      <c r="E13" s="26" t="inlineStr"/>
+      <c r="F13" s="26" t="inlineStr"/>
+      <c r="G13" s="26" t="n">
         <v>101.56</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>B) Amazon – nur wenn du KEINEN zweiten Shop willst (teurer, Händlerversand)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Pos</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>Teil</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Amazon-Titel</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>ASIN/Link</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="26" t="inlineStr">
         <is>
           <t>Variante wählen</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="26" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
         <is>
           <t>Packung</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>passt weil</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>Hinweis</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>P-MOSFET AO3401 (SOT-23)</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>Chanzon AO3401 SOT-23 P-Kanal 4A, 100 Stück</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B08LVLLC1V</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="26" t="inlineStr">
         <is>
           <t>100er</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="26" t="n">
         <v>18.99</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>100 Stk</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="26" t="inlineStr">
         <is>
           <t>AO3401 = gleiche Daten wie AO3401A (-30 V/-4 A, SOT-23)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="26" t="inlineStr">
         <is>
           <t>Versand durch Händler (Chanzon DE), Lieferung 23.–26.10.; günstiger: Reichelt 2×0,17 € + 5,95 € Versand</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Transistor BC547</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="C18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>Tyenaza BC-Transistor-Sortiment 200 Stk (BC327…BC558)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B097XRFK3H</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="26" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="26" t="n">
         <v>9.49</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
         <is>
           <t>200 Stk</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>enthält 20× BC547 (TO-92)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="26" t="inlineStr">
         <is>
           <t>Nur 8 auf Lager; „manuell sortiert“; nur nötig, wenn nicht bei Berrybase (0,17 €)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>Schiebeschalter C&amp;K OS102011MS2QN1</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="C19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
         <is>
           <t>C &amp; K os102011ms2qn1 Schiebeschalter SPDT On-On, 10 Stk</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B011NM291G</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>10er</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="26" t="n">
         <v>16.13</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>10 Stk</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Original-Teilenummer → passt exakt in die Wandtasche (8,6×4,3×4)</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="26" t="inlineStr">
         <is>
           <t>Händler HD TEC LTD, Lieferung 28.–31.10.; Seite widersprüchlich (ON-OFF/vertikal). Berrybase 0,70 € ist besser</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>C) Amazon – optional</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t>Pos</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>Teil</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="26" t="inlineStr">
         <is>
           <t>Amazon-Titel</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>ASIN/Link</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="26" t="inlineStr">
         <is>
           <t>Variante wählen</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="26" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
         <is>
           <t>Packung</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" s="26" t="inlineStr">
         <is>
           <t>passt weil</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="26" t="inlineStr">
         <is>
           <t>Hinweis</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>PLA weiß (Diffusor + Gehäuse)</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
         <is>
           <t>ELEGOO PLA 1,75 mm Weiß 1 kg</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B0CD7B7ZKK</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="26" t="inlineStr">
         <is>
           <t>Weiß, 1KG</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="26" t="n">
         <v>13.99</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>1 kg</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="26" t="inlineStr">
         <is>
           <t>weißes PLA für den Diffusor (ca. 128 g gesamt)</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="26" t="inlineStr">
         <is>
           <t>nur falls die Schule kein Filament stellt</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Schrumpfschlauch</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>QUADRIOS 800 tlg. Schrumpfschlauch 2:1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B07X27DFM5</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="26" t="inlineStr">
         <is>
           <t>schwarz/rot</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" s="26" t="n">
         <v>12.99</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>800 tlg.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="26" t="inlineStr">
         <is>
           <t>1,5–12 mm</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="26" t="inlineStr">
         <is>
           <t>optional, Berrybase 2,80 € reicht</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Doppelseitiges Schaumklebeband</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
         <is>
           <t>tesa Powerbond Ultra Strong 19 mm</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>https://www.amazon.de/dp/B0171QJJ4S</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="26" t="inlineStr">
         <is>
           <t>19 mm x 1500 mm wählen, falls günstiger (5 m = 15,95 €)</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="26" t="n">
         <v>15.95</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
         <is>
           <t>5 m</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="26" t="inlineStr">
         <is>
           <t>fixiert Pololu, HX711, LM393 in den Fächern</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="26" t="inlineStr">
         <is>
           <t>optional, Berrybase TESA 2,90 € reicht</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>D) Nicht (sinnvoll) bei Amazon → Berrybase (Preise vom 09.10.2026, vor Bestellung prüfen)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr"/>
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Teil</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>Menge</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr"/>
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="26" t="inlineStr"/>
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr"/>
+      <c r="I28" s="26" t="inlineStr"/>
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>Warum nicht Amazon</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>Pololu S13V10F5 5 V 1 A Step-Up/Down</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
+      <c r="C29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="26" t="inlineStr"/>
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/pololu-s13v10f5-5v-1a-step-up-step-down-converter</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="n">
+      <c r="F29" s="26" t="inlineStr"/>
+      <c r="G29" s="26" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr"/>
+      <c r="I29" s="26" t="inlineStr"/>
+      <c r="J29" s="26" t="inlineStr">
         <is>
           <t>Auf Amazon.de nicht gelistet (nur S9V11F5S6CMA, nicht verfügbar). TPS63020-Module: auf Amazon.de keine prüfbare Seite gefunden, 5 V nur ca. 0,9–1,3 A, Maße unbekannt → nicht empfohlen. Andere Shops: Eckstein 11,80 €, Botland 7,90 €</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Regensensor LM393</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
+      <c r="C30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="26" t="inlineStr"/>
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/regensensor-mit-digitalem-und-analogem-ausgang</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="n">
+      <c r="F30" s="26" t="inlineStr"/>
+      <c r="G30" s="26" t="n">
         <v>1.8</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
+      <c r="H30" s="26" t="inlineStr"/>
+      <c r="I30" s="26" t="inlineStr"/>
+      <c r="J30" s="26" t="inlineStr">
         <is>
           <t>AZDelivery 1er/3er/5er auf Amazon.de alle „derzeit nicht verfügbar“ (16.10.)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Schiebeschalter C&amp;K OS102011MS2QN1</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
+      <c r="C31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="26" t="inlineStr"/>
+      <c r="E31" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/schiebeschalter-printmontage-on-on-2-stellig-8.6x4.3x4mm-gerade</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="n">
+      <c r="F31" s="26" t="inlineStr"/>
+      <c r="G31" s="26" t="n">
         <v>0.7</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr"/>
+      <c r="I31" s="26" t="inlineStr"/>
+      <c r="J31" s="26" t="inlineStr">
         <is>
           <t>Amazon nur 10er für 16,13 €; generische SS12D00 (8,5×3,5) passen NICHT sicher in die Tasche</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>BC547B</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
+      <c r="C32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="26" t="inlineStr"/>
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/bc547b-bipolarer-transistor-npn-45v-100ma-to-92-3-pin</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
+      <c r="F32" s="26" t="inlineStr"/>
+      <c r="G32" s="26" t="n">
         <v>0.17</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="H32" s="26" t="inlineStr"/>
+      <c r="I32" s="26" t="inlineStr"/>
+      <c r="J32" s="26" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Widerstände 470 Ω, 4,7 kΩ, 2×47 kΩ, 3×10 kΩ</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
+      <c r="C33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="26" t="inlineStr"/>
+      <c r="E33" s="26" t="inlineStr">
         <is>
           <t>siehe Einkaufsliste_HydroDesk_guenstig.xlsx</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="n">
+      <c r="F33" s="26" t="inlineStr"/>
+      <c r="G33" s="26" t="n">
         <v>0.36</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
+      <c r="H33" s="26" t="inlineStr"/>
+      <c r="I33" s="26" t="inlineStr"/>
+      <c r="J33" s="26" t="inlineStr">
         <is>
           <t>Amazon-Sortimente: nicht verfügbar oder Lieferung erst Nov.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Elko 470 µF/25 V</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
+      <c r="C34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="26" t="inlineStr"/>
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/elektrolytkondensator-470-f-25v-1050c-1-radial-tht</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="n">
+      <c r="F34" s="26" t="inlineStr"/>
+      <c r="G34" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
+      <c r="H34" s="26" t="inlineStr"/>
+      <c r="I34" s="26" t="inlineStr"/>
+      <c r="J34" s="26" t="inlineStr">
         <is>
           <t>AZDelivery-Elko-Sortiment auf Amazon nicht verfügbar</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>2× SOT-23-Adapter</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr"/>
+      <c r="E35" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/smd-breakout-adapter-fuer-sot23-ssop10-msop10-10-pin-0-50mm-0-95mm</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="n">
+      <c r="F35" s="26" t="inlineStr"/>
+      <c r="G35" s="26" t="n">
         <v>0.64</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
+      <c r="H35" s="26" t="inlineStr"/>
+      <c r="I35" s="26" t="inlineStr"/>
+      <c r="J35" s="26" t="inlineStr">
         <is>
           <t>auf Amazon.de kein Angebot gefunden</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>D8</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Stiftleiste 1×20 RM 2,54</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
+      <c r="C36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="26" t="inlineStr"/>
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/stiftleiste-1x-20-polig-rm-2-54-gerade</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
+      <c r="F36" s="26" t="inlineStr"/>
+      <c r="G36" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="H36" s="26" t="inlineStr"/>
+      <c r="I36" s="26" t="inlineStr"/>
+      <c r="J36" s="26" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>D9</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>Lochrasterplatine</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
+      <c r="C37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="26" t="inlineStr"/>
+      <c r="E37" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/lochrasterplatine-9x15cm-mit-einseitiger-kupferauflage</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="n">
+      <c r="F37" s="26" t="inlineStr"/>
+      <c r="G37" s="26" t="n">
         <v>1.1</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="H37" s="26" t="inlineStr"/>
+      <c r="I37" s="26" t="inlineStr"/>
+      <c r="J37" s="26" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>D10</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>Vierlingslitze 4×0,14 mm², 5 m</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
+      <c r="C38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="26" t="inlineStr"/>
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>https://www.berrybase.de/vierlingslitze-isoliert-4x0-14mm-5m-farbe-blau-gelb-rot-gruen</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="n">
+      <c r="F38" s="26" t="inlineStr"/>
+      <c r="G38" s="26" t="n">
         <v>3.5</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="H38" s="26" t="inlineStr"/>
+      <c r="I38" s="26" t="inlineStr"/>
+      <c r="J38" s="26" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>Schrumpfschlauch, TESA-Klebeband, Kabelbinder</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
+      <c r="C39" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="26" t="inlineStr"/>
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>siehe Einkaufsliste_HydroDesk_guenstig.xlsx</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
+      <c r="F39" s="26" t="inlineStr"/>
+      <c r="G39" s="26" t="n">
         <v>6.3</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
+      <c r="H39" s="26" t="inlineStr"/>
+      <c r="I39" s="26" t="inlineStr"/>
+      <c r="J39" s="26" t="inlineStr">
         <is>
           <t>ersetzt Amazon Pos. 13+14</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr"/>
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>Summe Berrybase (+4,95 € Versand)</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="n">
+      <c r="C40" s="26" t="inlineStr"/>
+      <c r="D40" s="26" t="inlineStr"/>
+      <c r="E40" s="26" t="inlineStr"/>
+      <c r="F40" s="26" t="inlineStr"/>
+      <c r="G40" s="26" t="n">
         <v>24.82</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>E1</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>AO3401A (2 + 1 Reserve) – Reichelt</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr"/>
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>https://www.reichelt.de/de/de/shop/produkt/mosfet_p-ch_-30v_-4a_0_041r_sot-23-166486</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="n">
+      <c r="F41" s="26" t="inlineStr"/>
+      <c r="G41" s="26" t="n">
         <v>0.51</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
+      <c r="H41" s="26" t="inlineStr"/>
+      <c r="I41" s="26" t="inlineStr"/>
+      <c r="J41" s="26" t="inlineStr">
         <is>
           <t>Berrybase hat ihn nicht; Amazon-Alternative Pos. 9 (18,99 €)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>E2</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>microSD-Sniffer</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AliExpress / openelab.de (ca. 5,95 €, nicht geprüft)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>auf Amazon.de kein Angebot gefunden; ohne Sniffer an die SD-Slot-Pads löten</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
+      <c r="C42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="26" t="inlineStr"/>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>nicht bestellen</t>
+        </is>
+      </c>
+      <c r="F42" s="26" t="inlineStr"/>
+      <c r="G42" s="26" t="inlineStr"/>
+      <c r="H42" s="26" t="inlineStr"/>
+      <c r="I42" s="26" t="inlineStr"/>
+      <c r="J42" s="26" t="inlineStr">
+        <is>
+          <t>nicht bestellen, passt nicht. SD-Slot zeigt zur Frontwand (nur ca. 3,5 mm Luft); Sniffer würde ca. 35–40 mm herausstehen. GPIO18/19/23 direkt an den SD-Slot löten.</t>
+        </is>
+      </c>
+    </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
+      <c r="A44" s="26" t="inlineStr"/>
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>EMPFOHLEN: A + D + Reichelt (inkl. Versand)</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
+      <c r="C44" s="26" t="inlineStr"/>
+      <c r="D44" s="26" t="inlineStr"/>
+      <c r="E44" s="26" t="inlineStr"/>
+      <c r="F44" s="26" t="inlineStr"/>
+      <c r="G44" s="26" t="n">
         <v>137.79</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
+      <c r="A45" s="26" t="inlineStr"/>
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>Variante „möglichst viel Amazon“: A + B (Pololu, Regensensor, Kleinteile trotzdem Berrybase)</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="n">
+      <c r="C45" s="26" t="inlineStr"/>
+      <c r="D45" s="26" t="inlineStr"/>
+      <c r="E45" s="26" t="inlineStr"/>
+      <c r="F45" s="26" t="inlineStr"/>
+      <c r="G45" s="26" t="n">
         <v>175.07</v>
       </c>
     </row>

--- a/doku/Einkaufsliste_HydroDesk_guenstig.xlsx
+++ b/doku/Einkaufsliste_HydroDesk_guenstig.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preisvergleich" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Empfehlung" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon-Warenkorb" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tatsächliche Bestellung" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -19,11 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.000&quot; €&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00 €"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -91,8 +93,27 @@
       <i val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -129,8 +150,23 @@
         <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -153,6 +189,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -164,7 +214,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -319,6 +369,18 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="14" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10013,4 +10075,916 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" style="27" min="1" max="1"/>
+    <col width="21" customWidth="1" style="27" min="2" max="2"/>
+    <col width="72" customWidth="1" style="27" min="3" max="3"/>
+    <col width="8" customWidth="1" style="27" min="4" max="4"/>
+    <col width="11" customWidth="1" style="27" min="5" max="5"/>
+    <col width="9" customWidth="1" style="27" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>Tatsächliche Bestellung HydroDesk Base – 16.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>Gesamt 122,13 € (4 Belege). microSD-Sniffer und PLA nicht bestellt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Bestellnummer</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>Produktname</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>Menge</t>
+        </is>
+      </c>
+      <c r="E4" s="54" t="inlineStr">
+        <is>
+          <t>Summe (€)</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="inlineStr">
+        <is>
+          <t>Hinweis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>303-9574488-4297123</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Fastsaw CYD ESP32-2432S028R 2,8" Touch TFT ILI9341 (Entwicklungsboard)</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="56" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F5" s="55" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>303-9574488-4297123</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>TC4056 USB-C Lademodul mit Schutz (10er-Pack)</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="56" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F6" s="55" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>303-9574488-4297123</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>DIYmalls Wägezelle 5 kg + HX711</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="56" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="F7" s="55" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>303-9574488-4297123</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>FUNIANMAOYI Silikonmatte 40×30 cm, 1,2 mm (rutschfest)</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="56" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="F8" s="55" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="55" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>303-9574488-4297123</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>EEMB LP103454 LiPo 3,7 V 2000 mAh mit JST-PH</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="56" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F9" s="55" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>303-9574488-4297123</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>BTF-LIGHTING WS2812B FCOB COB-LED-Streifen 1 m, 160 LEDs/m, 5 mm</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="56" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F10" s="55" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>303-9574488-4297123</t>
+        </is>
+      </c>
+      <c r="C11" s="57" t="inlineStr">
+        <is>
+          <t>Versand (frei)</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E11" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="55" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="58" t="inlineStr">
+        <is>
+          <t>Summe Amazon</t>
+        </is>
+      </c>
+      <c r="B12" s="58" t="n"/>
+      <c r="C12" s="58" t="n"/>
+      <c r="D12" s="58" t="n"/>
+      <c r="E12" s="59" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="F12" s="58" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>TESA Doppelseitiges Klebeband 10 m × 12 mm, transparent, PP-Träger, lösungsmittelfrei</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F14" s="55" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>BC547B – Bipolarer Transistor, NPN, 45 V, 100 mA, TO-92, 3-pin</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="56" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F15" s="55" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C16" s="55" t="inlineStr">
+        <is>
+          <t>Vierlingslitze isoliert, 4×0,14 mm, 5 m – Farbe: blau, gelb, rot, grün</t>
+        </is>
+      </c>
+      <c r="D16" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F16" s="55" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>Elektrolytkondensator, 470 µF, 25 V, 105 °C, ±1 %, radial, THT</t>
+        </is>
+      </c>
+      <c r="D17" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F17" s="55" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t>FIX&amp;FASTEN Selbstklebender Fuß, rund, Ø oben 9,5 / unten 10 mm, Höhe 4,5 mm, Gummi, schwarz</t>
+        </is>
+      </c>
+      <c r="D18" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F18" s="55" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>Metallschichtwiderstand, 10,0 kΩ, 1/4 W, ±1 %, 0207, axial</t>
+        </is>
+      </c>
+      <c r="D19" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="56" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F19" s="55" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>Metallschichtwiderstand, 470,0 Ω, 1/4 W, ±1 %, 0207, axial</t>
+        </is>
+      </c>
+      <c r="D20" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="56" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F20" s="55" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>Metallschichtwiderstand, 47,0 kΩ, 1/4 W, ±1 %, 0207, axial</t>
+        </is>
+      </c>
+      <c r="D21" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F21" s="55" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>Metallschichtwiderstand, 4,7 kΩ, 1/4 W, ±1 %, 0207, axial</t>
+        </is>
+      </c>
+      <c r="D22" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="56" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="55" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>Lochrasterplatine, doppelseitig, 3×7 cm, 10 Stück</t>
+        </is>
+      </c>
+      <c r="D23" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F23" s="55" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t>Stiftleiste, 1×20-polig, RM 2,54, gerade</t>
+        </is>
+      </c>
+      <c r="D24" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F24" s="55" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
+        <is>
+          <t>Pololu S13V10F5 5 V, 1 A Step-Up/Step-Down Converter</t>
+        </is>
+      </c>
+      <c r="D25" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="56" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="F25" s="55" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C26" s="55" t="inlineStr">
+        <is>
+          <t>Regensensor mit digitalem und analogem Ausgang</t>
+        </is>
+      </c>
+      <c r="D26" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="56" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F26" s="55" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C27" s="55" t="inlineStr">
+        <is>
+          <t>Schiebeschalter, Printmontage, ON-ON, 2-stellig, 8,6×4,3×4 mm, gerade</t>
+        </is>
+      </c>
+      <c r="D27" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F27" s="55" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>SMD Breakout Adapter für SOT23 / SSOP10 / MSOP10, 10 Pin, 0,50 mm / 0,95 mm</t>
+        </is>
+      </c>
+      <c r="D28" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F28" s="55" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C29" s="55" t="inlineStr">
+        <is>
+          <t>Kabelbinder, UV-beständig, Nylon, 100 Stück (100×2,5 mm, transparent)</t>
+        </is>
+      </c>
+      <c r="D29" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="56" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F29" s="55" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>Schrumpfschlauch-Set, 100-teilig in Sortimentsbox, schwarz</t>
+        </is>
+      </c>
+      <c r="D30" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F30" s="55" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="55" t="inlineStr">
+        <is>
+          <t>Berrybase</t>
+        </is>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>1086360</t>
+        </is>
+      </c>
+      <c r="C31" s="57" t="inlineStr">
+        <is>
+          <t>Versand DHL Paket</t>
+        </is>
+      </c>
+      <c r="D31" s="55" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E31" s="56" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="F31" s="55" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="58" t="inlineStr">
+        <is>
+          <t>Summe Berrybase</t>
+        </is>
+      </c>
+      <c r="B32" s="58" t="n"/>
+      <c r="C32" s="58" t="n"/>
+      <c r="D32" s="58" t="n"/>
+      <c r="E32" s="59" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="F32" s="58" t="n"/>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t>alleschrauben.de</t>
+        </is>
+      </c>
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t>FASTON</t>
+        </is>
+      </c>
+      <c r="C34" s="55" t="inlineStr">
+        <is>
+          <t>Senkkopfschrauben M3×12 mit Innensechskant DIN 7991, Edelstahl A2</t>
+        </is>
+      </c>
+      <c r="D34" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" s="56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F34" s="55" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="55" t="inlineStr">
+        <is>
+          <t>alleschrauben.de</t>
+        </is>
+      </c>
+      <c r="B35" s="55" t="inlineStr">
+        <is>
+          <t>FASTON</t>
+        </is>
+      </c>
+      <c r="C35" s="55" t="inlineStr">
+        <is>
+          <t>Senkkopfschrauben M4×10 mit Innensechskant DIN 7991, Edelstahl A2</t>
+        </is>
+      </c>
+      <c r="D35" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="56" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F35" s="55" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="55" t="inlineStr">
+        <is>
+          <t>alleschrauben.de</t>
+        </is>
+      </c>
+      <c r="B36" s="55" t="inlineStr">
+        <is>
+          <t>FASTON</t>
+        </is>
+      </c>
+      <c r="C36" s="55" t="inlineStr">
+        <is>
+          <t>Senkkopfschrauben M5×12 mit Innensechskant DIN 7991, Edelstahl A2</t>
+        </is>
+      </c>
+      <c r="D36" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="56" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F36" s="55" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="55" t="inlineStr">
+        <is>
+          <t>alleschrauben.de</t>
+        </is>
+      </c>
+      <c r="B37" s="55" t="inlineStr">
+        <is>
+          <t>FASTON</t>
+        </is>
+      </c>
+      <c r="C37" s="57" t="inlineStr">
+        <is>
+          <t>Versand</t>
+        </is>
+      </c>
+      <c r="D37" s="55" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E37" s="56" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F37" s="55" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="58" t="inlineStr">
+        <is>
+          <t>Summe alleschrauben.de</t>
+        </is>
+      </c>
+      <c r="B38" s="58" t="n"/>
+      <c r="C38" s="58" t="n"/>
+      <c r="D38" s="58" t="n"/>
+      <c r="E38" s="59" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="F38" s="58" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="55" t="inlineStr">
+        <is>
+          <t>Reichelt</t>
+        </is>
+      </c>
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="C40" s="55" t="inlineStr">
+        <is>
+          <t>MOSFET P-CH −30 V / −4 A, 0,041 Ω, SOT-23 (AO3401A)</t>
+        </is>
+      </c>
+      <c r="D40" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="56" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F40" s="55" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="55" t="inlineStr">
+        <is>
+          <t>Reichelt</t>
+        </is>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="C41" s="57" t="inlineStr">
+        <is>
+          <t>Versand DHL</t>
+        </is>
+      </c>
+      <c r="D41" s="55" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E41" s="56" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="F41" s="55" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="58" t="inlineStr">
+        <is>
+          <t>Summe Reichelt</t>
+        </is>
+      </c>
+      <c r="B42" s="58" t="n"/>
+      <c r="C42" s="58" t="n"/>
+      <c r="D42" s="58" t="n"/>
+      <c r="E42" s="59" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F42" s="58" t="n"/>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="60" t="inlineStr">
+        <is>
+          <t>GESAMT</t>
+        </is>
+      </c>
+      <c r="B44" s="60" t="n"/>
+      <c r="C44" s="60" t="inlineStr">
+        <is>
+          <t>69,52 + 35,46 + 10,35 + 6,80</t>
+        </is>
+      </c>
+      <c r="D44" s="60" t="n"/>
+      <c r="E44" s="61" t="n">
+        <v>122.13</v>
+      </c>
+      <c r="F44" s="60" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Nicht bestellt: microSD-Sniffer (passt nicht), PLA (Schule/Betrieb).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A46:F46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>